--- a/results/Int All Data 1.0/Linea_fi_all.xlsx
+++ b/results/Int All Data 1.0/Linea_fi_all.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.0007367387033398898 +/- 0.0004528263485900214</t>
+          <t>0.0006876227897838927 +/- 0.00039292730844792676</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.0012035583464155343 +/- 0.00155319958970757</t>
+          <t>-0.0010989010989011505 +/- 0.0014128728414442774</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.005075876504447974 +/- 0.001385473814220148</t>
+          <t>-0.005232862375719571 +/- 0.0014800769883548904</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>0.3203035060177917 +/- 0.006686811912228093</t>
+          <t>0.3203558346415488 +/- 0.006614139323631586</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.00021186440677966044 +/- 0.0007768361581921119</t>
+          <t>0.0003531073446327637 +/- 0.0007895720259533251</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0003382187147689231 +/- 0.0010146561443066643</t>
+          <t>0.00039458850056374174 +/- 0.00100994773772092</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.0025930101465614806 +/- 0.0013853670493173113</t>
+          <t>0.0026493799323562993 +/- 0.001471024616764374</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.008424242424242435 +/- 0.001981549421123827</t>
+          <t>0.008363636363636373 +/- 0.001873893919241219</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.0007878787878787929 +/- 0.0005454545454545489</t>
+          <t>0.000666666666666671 +/- 0.0005034317492677654</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -6221,72 +6221,72 @@
       </c>
       <c r="BW8" t="inlineStr">
         <is>
+          <t>0.0005913978494623384 +/- 0.0005072032866697005</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>0.01758064516129032 +/- 0.002416964171289137</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0.0018279569892473036 +/- 0.0009060376100189522</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>0.0018279569892473036 +/- 0.0009060376100189522</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>0.004569892473118275 +/- 0.0017545342873205006</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>0.036827956989247304 +/- 0.0030436945924125105</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>0.006236559139784936 +/- 0.001080631787217295</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>0.023279569892473116 +/- 0.003542272346242831</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>0.0005376344086021722 +/- 0.0010752688172043113</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>0.004032258064516114 +/- 0.0014275180696076985</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>0.5176344086021505 +/- 0.01220276149637274</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>0.002849462365591393 +/- 0.0009012394953892542</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>0.3901612903225806 +/- 0.012495923719679428</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
           <t>0.000645161290322549 +/- 0.0004023287512660202</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>0.01758064516129032 +/- 0.002416964171289137</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.0018279569892473036 +/- 0.0009060376100189522</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>0.0018279569892473036 +/- 0.0009060376100189522</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>0.004569892473118275 +/- 0.0017545342873205006</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>0.036827956989247304 +/- 0.0030436945924125105</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>0.006236559139784936 +/- 0.001080631787217295</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0.023279569892473116 +/- 0.003542272346242831</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>0.0005376344086021722 +/- 0.0010752688172043113</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>0.004086021505376336 +/- 0.0015053763440860148</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>0.5176344086021505 +/- 0.01220276149637274</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>0.002849462365591393 +/- 0.0009012394953892542</t>
-        </is>
-      </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>0.3901612903225806 +/- 0.012495923719679428</t>
-        </is>
-      </c>
-      <c r="CJ8" t="inlineStr">
-        <is>
-          <t>0.0005913978494623384 +/- 0.0005072032866697005</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.0032813340505648547 +/- 0.0013055041527177574</t>
+          <t>-0.002366863905325478 +/- 0.0005485766017851639</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.014470145239376054 +/- 0.0013703861433950627</t>
+          <t>-0.011296395911780555 +/- 0.0013394189992456968</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.00037654653039270736 +/- 0.001077191199273845</t>
+          <t>-0.00043033889187737984 +/- 0.0010971532035702624</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0018289402904787199 +/- 0.0017213555675093983</t>
+          <t>-0.000806885422270065 +/- 0.0014484036597994842</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.011403980634749811 +/- 0.0024509490586109833</t>
+          <t>0.00021516944593864552 +/- 0.00026352767539352583</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.0044647660032275825 +/- 0.0022573572090755626</t>
+          <t>-0.001398601398601429 +/- 0.000493015136627829</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-0.0079074771382464 +/- 0.0023330014461755196</t>
+          <t>-0.00839160839160843 +/- 0.0009065249890453466</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.0005379236148467137 +/- 0.001128358093781761</t>
+          <t>-0.00043033889187737984 +/- 0.0010971532035702624</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.007530930607853714 +/- 0.0021784246079953316</t>
+          <t>-0.013232920925228642 +/- 0.0017710680616626591</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -6771,17 +6771,17 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.00016137708445397304 +/- 0.0006387489019385591</t>
+          <t>0.006024744486282907 +/- 0.001645729805355384</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.005271651425497526 +/- 0.0019064061481085985</t>
+          <t>0.0005379236148466693 +/- 0.0007217002616997653</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.0002689618074233846 +/- 0.0005512076797181078</t>
+          <t>-4.4408920985006264e-17 +/- 0.000931711031505569</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.015008068854222668 +/- 0.0028203822977769235</t>
+          <t>0.0005379236148466582 +/- 0.0012500215210997391</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.006132329209252318 +/- 0.0020299044931805397</t>
+          <t>0.0039268423883808135 +/- 0.0018486111110747091</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.017482517482517456 +/- 0.001636030804276014</t>
+          <t>0.002904787520172114 +/- 0.0017380843917593992</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.003980634749865564 +/- 0.001207635520206755</t>
+          <t>0.0005379236148466693 +/- 0.0007217002616997653</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.013448090371167254 +/- 0.0026352767539356324</t>
+          <t>-0.00796126949973106 +/- 0.0012219275623023913</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.013125336202259308 +/- 0.002420058500097258</t>
+          <t>-0.005809575040344317 +/- 0.0015176692823739525</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.007477138246368986 +/- 0.0020334651072012816</t>
+          <t>0.0009682625067240158 +/- 0.000956233934084516</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.0022054868208714606 +/- 0.0005074761232951685</t>
+          <t>-0.008122646584185078 +/- 0.0017751479289940747</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.0008606777837546487 +/- 0.00043033889187737984</t>
+          <t>-0.004464766003227594 +/- 0.0011296395911780588</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>5.3792361484650274e-05 +/- 0.00028968073195987867</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.013179128563743925 +/- 0.0025937737388361847</t>
+          <t>-0.002259279182356133 +/- 0.0007905830261807031</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.0009682625067240824 +/- 0.0006273213442544763</t>
+          <t>0.0009682625067240158 +/- 0.000956233934084516</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.016837009144701397 +/- 0.0010499850078506301</t>
+          <t>-0.0026896180742335017 +/- 0.0010206382980640378</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.0010758472296934385 +/- 0.0009317110315055817</t>
+          <t>0.003980634749865475 +/- 0.0028280665794717503</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -7001,17 +7001,17 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>0.05836471221086603 +/- 0.002648966595426594</t>
+          <t>-0.002097902097902138 +/- 0.0018391953735641545</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.013770844540075267 +/- 0.0025708021829690406</t>
+          <t>0.0004841312533619857 +/- 0.0006109637811511785</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.0007530930607853259 +/- 0.0019720605465114046</t>
+          <t>0.0004841312533619857 +/- 0.0006109637811511785</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.02033351264120491 +/- 0.003180579989046699</t>
+          <t>-0.002151694459386788 +/- 0.0020972123388507814</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.003657880580957551 +/- 0.00236686390532544</t>
+          <t>-0.0004841312533620523 +/- 0.0002896807319599158</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.12883270575578262 +/- 0.005465949820576005</t>
+          <t>-0.0010220548682087437 +/- 0.0006109637811511815</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -7086,227 +7086,227 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
+          <t>0.0024744486282947454 +/- 0.0008402635477037924</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>-4.4408920985006264e-17 +/- 0.0007217002616997653</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>0.06508875739644965 +/- 0.004180604459973204</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>0.06686390532544376 +/- 0.0051710661726585465</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>0.19392146315223238 +/- 0.007392291853013385</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>0.12017213555675091 +/- 0.0032382822901113346</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>0.005217859064012853 +/- 0.0018010402412892105</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>0.027057557826788557 +/- 0.0033683641106946223</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>-0.004841312533620246 +/- 0.001751352404098955</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>-0.011027434104357225 +/- 0.0026380204056458737</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>0.0004841312533619857 +/- 0.0006566194521642371</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>0.039214631522323795 +/- 0.0028408275258764676</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>0.4057557826788596 +/- 0.01116771400331099</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>-0.0022054868208714494 +/- 0.0006566194521642798</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>0.04201183431952658 +/- 0.0024110742152786426</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>0.19392146315223238 +/- 0.007392291853013385</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>0.00032275416890796825 +/- 0.00253681035450278</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>0.00016137708445396193 +/- 0.00048413125336200916</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>-0.010704679935449223 +/- 0.0014917078670104347</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>0.0008068854222699762 +/- 0.00036085013084990753</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>0.0003765465303926296 +/- 0.00024650756831388784</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>-0.00016137708445401744 +/- 0.00024650756831393875</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>-0.00016137708445402855 +/- 0.0007996809439116948</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>0.0009682625067240047 +/- 0.0007905830261806894</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>0.00016137708445396193 +/- 0.0008350820170123783</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>0.0016137708445400412 +/- 0.0005892657961325035</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>0.00010758472296931165 +/- 0.0003227541689079905</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>-0.000322754168908046 +/- 0.000688878347222454</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>0.0005379236148466248 +/- 0.00024056675389991355</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>0.013394298009682592 +/- 0.0022367534035816873</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>-0.0003227541689080571 +/- 0.0005485766017851289</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>-0.00016137708445401744 +/- 0.00024650756831393875</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>0.0009682625067240047 +/- 0.0007905830261806894</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>0.013232920925228587 +/- 0.0015627583696970389</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
           <t>0.0006455083378159587 +/- 0.00021516944593868995</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>-4.4408920985006264e-17 +/- 0.0007217002616997653</t>
-        </is>
-      </c>
-      <c r="CQ9" t="inlineStr">
-        <is>
-          <t>0.06508875739644965 +/- 0.004180604459973204</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>0.03830016137708442 +/- 0.0037792723120495387</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>0.19268423883808494 +/- 0.007390530175619415</t>
-        </is>
-      </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>0.13910704679935448 +/- 0.005024333266846965</t>
-        </is>
-      </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>0.005217859064012853 +/- 0.0018010402412892105</t>
-        </is>
-      </c>
-      <c r="CV9" t="inlineStr">
-        <is>
-          <t>0.027057557826788557 +/- 0.0033683641106946223</t>
-        </is>
-      </c>
-      <c r="CW9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>-0.0034965034965035446 +/- 0.002444447072082136</t>
-        </is>
-      </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>0.0006993006993006312 +/- 0.00024650756831393875</t>
-        </is>
-      </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0.0004841312533619857 +/- 0.0006566194521642371</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DB9" t="inlineStr">
-        <is>
-          <t>0.033781603012372194 +/- 0.0023049257972704027</t>
-        </is>
-      </c>
-      <c r="DC9" t="inlineStr">
-        <is>
-          <t>0.4057557826788596 +/- 0.01116771400331099</t>
-        </is>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>-0.0022054868208714494 +/- 0.0006566194521642798</t>
-        </is>
-      </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>0.04201183431952658 +/- 0.0024110742152786426</t>
-        </is>
-      </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>0.1953738569123184 +/- 0.007074462495007467</t>
-        </is>
-      </c>
-      <c r="DG9" t="inlineStr">
-        <is>
-          <t>0.00032275416890796825 +/- 0.00253681035450278</t>
-        </is>
-      </c>
-      <c r="DH9" t="inlineStr">
-        <is>
-          <t>0.00016137708445396193 +/- 0.00048413125336200916</t>
-        </is>
-      </c>
-      <c r="DI9" t="inlineStr">
-        <is>
-          <t>-0.010704679935449223 +/- 0.0014917078670104347</t>
-        </is>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>0.0008068854222699762 +/- 0.00036085013084990753</t>
-        </is>
-      </c>
-      <c r="DK9" t="inlineStr">
-        <is>
-          <t>0.0018289402904787199 +/- 0.00035681815926360064</t>
-        </is>
-      </c>
-      <c r="DL9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DM9" t="inlineStr">
-        <is>
-          <t>-0.00016137708445401744 +/- 0.00024650756831393875</t>
-        </is>
-      </c>
-      <c r="DN9" t="inlineStr">
-        <is>
-          <t>0.0013448090371166788 +/- 0.0008068854222700279</t>
-        </is>
-      </c>
-      <c r="DO9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>0.004249596557288826 +/- 0.0017751479289940819</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>5.379236148466138e-05 +/- 0.00016137708445398413</t>
-        </is>
-      </c>
-      <c r="DR9" t="inlineStr">
-        <is>
-          <t>-0.00043033889187739095 +/- 0.00032275416890800154</t>
-        </is>
-      </c>
-      <c r="DS9" t="inlineStr">
-        <is>
-          <t>0.0016137708445400412 +/- 0.0005892657961325035</t>
-        </is>
-      </c>
-      <c r="DT9" t="inlineStr">
-        <is>
-          <t>0.0008068854222699984 +/- 0.00115997087965828</t>
-        </is>
-      </c>
-      <c r="DU9" t="inlineStr">
-        <is>
-          <t>0.004303388918773521 +/- 0.0012028337694996222</t>
-        </is>
-      </c>
-      <c r="DV9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DW9" t="inlineStr">
-        <is>
-          <t>-0.000322754168908046 +/- 0.000688878347222454</t>
-        </is>
-      </c>
-      <c r="DX9" t="inlineStr">
-        <is>
-          <t>-0.0009144701452394211 +/- 0.00034443917361123307</t>
-        </is>
-      </c>
-      <c r="DY9" t="inlineStr">
-        <is>
-          <t>0.013394298009682592 +/- 0.0022367534035816873</t>
-        </is>
-      </c>
-      <c r="DZ9" t="inlineStr">
-        <is>
-          <t>-0.0003227541689080571 +/- 0.0005485766017851289</t>
-        </is>
-      </c>
-      <c r="EA9" t="inlineStr">
-        <is>
-          <t>-0.00016137708445401744 +/- 0.00024650756831393875</t>
-        </is>
-      </c>
-      <c r="EB9" t="inlineStr">
-        <is>
-          <t>0.006455083378160265 +/- 0.002711049632781975</t>
-        </is>
-      </c>
-      <c r="EC9" t="inlineStr">
-        <is>
-          <t>0.013232920925228587 +/- 0.0015627583696970389</t>
-        </is>
-      </c>
-      <c r="ED9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>0.0006455083378159587 +/- 0.00021516944593868995</t>
-        </is>
-      </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>-0.0020441097364174545 +/- 0.0005270553507871401</t>
+          <t>0.0003765465303926296 +/- 0.00024650756831388784</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>0.00161377084454003 +/- 0.0004166738403665686</t>
+          <t>0.0006993006993006423 +/- 0.00034443917361123307</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>-0.0006455083378160698 +/- 0.0003227541689080349</t>
+          <t>-0.002689618074233513 +/- 0.0005379236148467248</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>-0.0004841312533620523 +/- 0.0005616087417380527</t>
+          <t>-1.1102230246251566e-17 +/- 0.00024056675389991355</t>
         </is>
       </c>
       <c r="EN9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-1.1102230246251566e-17 +/- 0.00024056675389991355</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>0.0020441097364173877 +/- 0.000627321344254461</t>
+          <t>0.0003765465303926296 +/- 0.00024650756831388784</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>-0.00010758472296934496 +/- 0.00021516944593868995</t>
+          <t>0.0006993006993006423 +/- 0.00034443917361123307</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>-0.004195804195804231 +/- 0.0005793614639197904</t>
+          <t>-0.002689618074233513 +/- 0.0005379236148467248</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.06305991855730075 +/- 0.005876372914100927</t>
+          <t>0.06294357184409541 +/- 0.005827797457297577</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="EB11" t="inlineStr">
         <is>
-          <t>-0.02165775401069524 +/- 0.005444312515176205</t>
+          <t>-0.021711229946524115 +/- 0.005433534030323223</t>
         </is>
       </c>
       <c r="EC11" t="inlineStr">
